--- a/data/plejd_vs_electrician_trends.xlsx
+++ b/data/plejd_vs_electrician_trends.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,87 +429,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Sweden_Plejd</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Sweden_elektriker</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Norway_Plejd</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Norway_elektriker</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Finland_Plejd</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Finland_sähköasentaja</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Netherlands_Plejd</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Netherlands_elektricien</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Germany_Plejd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Germany_Elektriker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -505,15 +517,15 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>42</v>
@@ -522,13 +534,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -536,30 +548,30 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B4" t="n">
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -567,18 +579,18 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -590,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -598,30 +610,30 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -629,30 +641,30 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>58</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>38</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -664,11 +676,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>32</v>
@@ -677,13 +689,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -695,7 +707,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B9" t="n">
@@ -708,13 +720,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -722,18 +734,18 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -745,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -753,15 +765,15 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>44</v>
@@ -770,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -784,11 +796,11 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B12" t="n">
@@ -801,13 +813,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -815,30 +827,30 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B13" t="n">
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -846,15 +858,15 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>42</v>
@@ -869,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -877,11 +889,11 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B15" t="n">
@@ -894,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -908,30 +920,30 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -939,11 +951,11 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B17" t="n">
@@ -962,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -970,11 +982,11 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B18" t="n">
@@ -987,13 +999,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1001,30 +1013,30 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1032,11 +1044,11 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B20" t="n">
@@ -1063,30 +1075,30 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B21" t="n">
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1094,11 +1106,11 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B22" t="n">
@@ -1111,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1125,11 +1137,11 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B23" t="n">
@@ -1148,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1156,11 +1168,11 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B24" t="n">
@@ -1187,30 +1199,30 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1218,11 +1230,11 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B26" t="n">
@@ -1249,30 +1261,30 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1280,11 +1292,11 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B28" t="n">
@@ -1297,13 +1309,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1311,11 +1323,11 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B29" t="n">
@@ -1328,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1342,11 +1354,11 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B30" t="n">
@@ -1359,13 +1371,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1373,30 +1385,30 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1408,14 +1420,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1427,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1435,15 +1447,15 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="n">
         <v>43</v>
@@ -1452,13 +1464,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1466,11 +1478,11 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B34" t="n">
@@ -1483,13 +1495,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1501,7 +1513,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B35" t="n">
@@ -1514,13 +1526,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1528,30 +1540,30 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C36" t="n">
+        <v>47</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>77</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
         <v>46</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>76</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>49</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1559,30 +1571,30 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B37" t="n">
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1590,24 +1602,24 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C38" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1621,11 +1633,11 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B39" t="n">
@@ -1638,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1652,11 +1664,11 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B40" t="n">
@@ -1669,13 +1681,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1683,11 +1695,11 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B41" t="n">
@@ -1697,10 +1709,10 @@
         <v>43</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1714,11 +1726,11 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B42" t="n">
@@ -1731,13 +1743,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1745,18 +1757,18 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1768,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1776,11 +1788,11 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B44" t="n">
@@ -1793,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1807,30 +1819,30 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B45" t="n">
         <v>17</v>
       </c>
       <c r="C45" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1838,30 +1850,30 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B46" t="n">
         <v>22</v>
       </c>
       <c r="C46" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1869,11 +1881,11 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B47" t="n">
@@ -1892,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1900,11 +1912,11 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B48" t="n">
@@ -1917,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1931,15 +1943,15 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C49" t="n">
         <v>42</v>
@@ -1948,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1962,27 +1974,27 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C50" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
         <v>51</v>
@@ -1993,11 +2005,11 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B51" t="n">
@@ -2010,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2024,27 +2036,27 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B52" t="n">
         <v>19</v>
       </c>
       <c r="C52" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>46</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>39</v>
@@ -2059,26 +2071,26 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B53" t="n">
         <v>21</v>
       </c>
       <c r="C53" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -2086,11 +2098,11 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B54" t="n">
@@ -2100,16 +2112,16 @@
         <v>42</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -2117,30 +2129,30 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B55" t="n">
         <v>17</v>
       </c>
       <c r="C55" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2148,24 +2160,24 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B56" t="n">
         <v>22</v>
       </c>
       <c r="C56" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2179,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B57" t="n">
         <v>24</v>
       </c>
       <c r="C57" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2202,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -2210,30 +2222,30 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B58" t="n">
         <v>31</v>
       </c>
       <c r="C58" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
         <v>84</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2241,11 +2253,11 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B59" t="n">
@@ -2258,13 +2270,13 @@
         <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -2272,15 +2284,15 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B60" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C60" t="n">
         <v>54</v>
@@ -2289,13 +2301,13 @@
         <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2303,30 +2315,30 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B61" t="n">
         <v>40</v>
       </c>
       <c r="C61" t="n">
+        <v>51</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" t="n">
+        <v>65</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="n">
         <v>49</v>
-      </c>
-      <c r="D61" t="n">
-        <v>5</v>
-      </c>
-      <c r="E61" t="n">
-        <v>64</v>
-      </c>
-      <c r="F61" t="n">
-        <v>7</v>
-      </c>
-      <c r="G61" t="n">
-        <v>46</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2334,50 +2346,50 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B62" t="n">
         <v>35</v>
       </c>
       <c r="C62" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F62" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C63" t="n">
         <v>51</v>
@@ -2386,10 +2398,10 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G63" t="n">
         <v>60</v>
@@ -2404,11 +2416,11 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B64" t="n">
@@ -2421,33 +2433,33 @@
         <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C65" t="n">
         <v>49</v>
@@ -2456,29 +2468,29 @@
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F65" t="n">
         <v>5</v>
       </c>
       <c r="G65" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B66" t="n">
@@ -2497,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2509,15 +2521,15 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C67" t="n">
         <v>47</v>
@@ -2526,39 +2538,39 @@
         <v>4</v>
       </c>
       <c r="E67" t="n">
+        <v>71</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>45</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
         <v>70</v>
       </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>40</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>71</v>
-      </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B68" t="n">
         <v>27</v>
       </c>
       <c r="C68" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
         <v>63</v>
@@ -2567,93 +2579,93 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
+        <v>77</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>78</v>
       </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C69" t="n">
         <v>53</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G69" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B70" t="n">
         <v>33</v>
       </c>
       <c r="C70" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F70" t="n">
         <v>6</v>
       </c>
       <c r="G70" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B71" t="n">
@@ -2666,13 +2678,13 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2684,123 +2696,123 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B72" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C72" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D72" t="n">
         <v>10</v>
       </c>
       <c r="E72" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F72" t="n">
+        <v>9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>46</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>74</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B73" t="n">
+        <v>37</v>
+      </c>
+      <c r="C73" t="n">
+        <v>47</v>
+      </c>
+      <c r="D73" t="n">
         <v>10</v>
       </c>
-      <c r="G72" t="n">
-        <v>45</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>76</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B73" t="n">
-        <v>39</v>
-      </c>
-      <c r="C73" t="n">
-        <v>46</v>
-      </c>
-      <c r="D73" t="n">
-        <v>11</v>
-      </c>
       <c r="E73" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
+        <v>72</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>71</v>
       </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>72</v>
-      </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C74" t="n">
         <v>54</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G74" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B75" t="n">
         <v>42</v>
       </c>
       <c r="C75" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D75" t="n">
         <v>11</v>
@@ -2809,7 +2821,7 @@
         <v>87</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>61</v>
@@ -2818,68 +2830,68 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B76" t="n">
         <v>30</v>
       </c>
       <c r="C76" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D76" t="n">
         <v>11</v>
       </c>
       <c r="E76" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G76" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C77" t="n">
         <v>48</v>
       </c>
       <c r="D77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
         <v>53</v>
@@ -2888,33 +2900,33 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B78" t="n">
         <v>25</v>
       </c>
       <c r="C78" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E78" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G78" t="n">
         <v>54</v>
@@ -2923,68 +2935,68 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B79" t="n">
         <v>23</v>
       </c>
       <c r="C79" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D79" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" t="n">
+        <v>69</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>49</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>56</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B80" t="n">
+        <v>26</v>
+      </c>
+      <c r="C80" t="n">
+        <v>47</v>
+      </c>
+      <c r="D80" t="n">
         <v>9</v>
-      </c>
-      <c r="E79" t="n">
-        <v>68</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>50</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>57</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>44773</v>
-      </c>
-      <c r="B80" t="n">
-        <v>25</v>
-      </c>
-      <c r="C80" t="n">
-        <v>46</v>
-      </c>
-      <c r="D80" t="n">
-        <v>8</v>
       </c>
       <c r="E80" t="n">
         <v>61</v>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>46</v>
@@ -2993,56 +3005,56 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B81" t="n">
         <v>37</v>
       </c>
       <c r="C81" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E81" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C82" t="n">
         <v>58</v>
@@ -3051,16 +3063,16 @@
         <v>14</v>
       </c>
       <c r="E82" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
         <v>74</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>57</v>
@@ -3069,15 +3081,15 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C83" t="n">
         <v>61</v>
@@ -3086,13 +3098,13 @@
         <v>19</v>
       </c>
       <c r="E83" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F83" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3104,68 +3116,68 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B84" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C84" t="n">
         <v>57</v>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E84" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G84" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C85" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D85" t="n">
         <v>18</v>
       </c>
       <c r="E85" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F85" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G85" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>71</v>
@@ -3178,23 +3190,23 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C86" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D86" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E86" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G86" t="n">
         <v>64</v>
@@ -3203,17 +3215,17 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B87" t="n">
@@ -3223,32 +3235,32 @@
         <v>55</v>
       </c>
       <c r="D87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E87" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G87" t="n">
         <v>64</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B88" t="n">
@@ -3261,7 +3273,7 @@
         <v>18</v>
       </c>
       <c r="E88" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F88" t="n">
         <v>8</v>
@@ -3270,7 +3282,7 @@
         <v>65</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>57</v>
@@ -3279,30 +3291,30 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B89" t="n">
         <v>28</v>
       </c>
       <c r="C89" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E89" t="n">
         <v>63</v>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3314,33 +3326,33 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C90" t="n">
         <v>54</v>
       </c>
       <c r="D90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E90" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F90" t="n">
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
         <v>52</v>
@@ -3349,11 +3361,11 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B91" t="n">
@@ -3363,39 +3375,39 @@
         <v>51</v>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E91" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F91" t="n">
         <v>5</v>
       </c>
       <c r="G91" t="n">
+        <v>53</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>54</v>
       </c>
-      <c r="H91" t="n">
-        <v>1</v>
-      </c>
-      <c r="I91" t="n">
-        <v>55</v>
-      </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B92" t="n">
         <v>26</v>
       </c>
       <c r="C92" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D92" t="n">
         <v>17</v>
@@ -3404,10 +3416,10 @@
         <v>63</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G92" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
@@ -3419,33 +3431,33 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C93" t="n">
         <v>52</v>
       </c>
       <c r="D93" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E93" t="n">
         <v>80</v>
       </c>
       <c r="F93" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
         <v>49</v>
@@ -3454,11 +3466,11 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B94" t="n">
@@ -3471,71 +3483,71 @@
         <v>25</v>
       </c>
       <c r="E94" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F94" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G94" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C95" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D95" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E95" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G95" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C96" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D96" t="n">
         <v>40</v>
@@ -3544,115 +3556,115 @@
         <v>81</v>
       </c>
       <c r="F96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G96" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B97" t="n">
         <v>50</v>
       </c>
       <c r="C97" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D97" t="n">
         <v>30</v>
       </c>
       <c r="E97" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G97" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D98" t="n">
         <v>28</v>
       </c>
       <c r="E98" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H98" t="n">
         <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C99" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D99" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E99" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G99" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
@@ -3664,46 +3676,46 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B100" t="n">
         <v>35</v>
       </c>
       <c r="C100" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D100" t="n">
         <v>29</v>
       </c>
       <c r="E100" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F100" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G100" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B101" t="n">
@@ -3716,13 +3728,13 @@
         <v>24</v>
       </c>
       <c r="E101" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F101" t="n">
         <v>13</v>
       </c>
       <c r="G101" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -3734,33 +3746,33 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B102" t="n">
         <v>28</v>
       </c>
       <c r="C102" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D102" t="n">
         <v>19</v>
       </c>
       <c r="E102" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G102" t="n">
         <v>56</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
         <v>51</v>
@@ -3769,11 +3781,11 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B103" t="n">
@@ -3786,13 +3798,13 @@
         <v>27</v>
       </c>
       <c r="E103" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F103" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G103" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H103" t="n">
         <v>2</v>
@@ -3804,81 +3816,81 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B104" t="n">
         <v>29</v>
       </c>
       <c r="C104" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D104" t="n">
         <v>25</v>
       </c>
       <c r="E104" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G104" t="n">
         <v>46</v>
       </c>
       <c r="H104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I104" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C105" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D105" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E105" t="n">
         <v>83</v>
       </c>
       <c r="F105" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G105" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I105" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B106" t="n">
@@ -3888,57 +3900,57 @@
         <v>53</v>
       </c>
       <c r="D106" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E106" t="n">
         <v>89</v>
       </c>
       <c r="F106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G106" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H106" t="n">
         <v>4</v>
       </c>
       <c r="I106" t="n">
+        <v>59</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B107" t="n">
+        <v>65</v>
+      </c>
+      <c r="C107" t="n">
+        <v>59</v>
+      </c>
+      <c r="D107" t="n">
+        <v>47</v>
+      </c>
+      <c r="E107" t="n">
+        <v>91</v>
+      </c>
+      <c r="F107" t="n">
+        <v>19</v>
+      </c>
+      <c r="G107" t="n">
         <v>61</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>45596</v>
-      </c>
-      <c r="B107" t="n">
-        <v>64</v>
-      </c>
-      <c r="C107" t="n">
-        <v>58</v>
-      </c>
-      <c r="D107" t="n">
-        <v>46</v>
-      </c>
-      <c r="E107" t="n">
-        <v>90</v>
-      </c>
-      <c r="F107" t="n">
-        <v>22</v>
-      </c>
-      <c r="G107" t="n">
-        <v>63</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
       </c>
       <c r="I107" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -3948,42 +3960,42 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C108" t="n">
         <v>55</v>
       </c>
       <c r="D108" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E108" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G108" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I108" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B109" t="n">
@@ -3993,7 +4005,7 @@
         <v>45</v>
       </c>
       <c r="D109" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E109" t="n">
         <v>66</v>
@@ -4002,128 +4014,128 @@
         <v>16</v>
       </c>
       <c r="G109" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H109" t="n">
         <v>5</v>
       </c>
       <c r="I109" t="n">
+        <v>57</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B110" t="n">
+        <v>53</v>
+      </c>
+      <c r="C110" t="n">
         <v>59</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B110" t="n">
-        <v>52</v>
-      </c>
-      <c r="C110" t="n">
-        <v>58</v>
       </c>
       <c r="D110" t="n">
         <v>56</v>
       </c>
       <c r="E110" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G110" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H110" t="n">
         <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B111" t="n">
+        <v>54</v>
+      </c>
+      <c r="C111" t="n">
+        <v>58</v>
+      </c>
+      <c r="D111" t="n">
+        <v>53</v>
+      </c>
+      <c r="E111" t="n">
         <v>93</v>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B111" t="n">
-        <v>51</v>
-      </c>
-      <c r="C111" t="n">
-        <v>56</v>
-      </c>
-      <c r="D111" t="n">
-        <v>50</v>
-      </c>
-      <c r="E111" t="n">
-        <v>89</v>
-      </c>
       <c r="F111" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G111" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H111" t="n">
         <v>5</v>
       </c>
       <c r="I111" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B112" t="n">
         <v>43</v>
       </c>
       <c r="C112" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D112" t="n">
         <v>50</v>
       </c>
       <c r="E112" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F112" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G112" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H112" t="n">
         <v>5</v>
       </c>
       <c r="I112" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B113" t="n">
@@ -4133,16 +4145,16 @@
         <v>48</v>
       </c>
       <c r="D113" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E113" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F113" t="n">
         <v>16</v>
       </c>
       <c r="G113" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H113" t="n">
         <v>4</v>
@@ -4154,33 +4166,33 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B114" t="n">
         <v>42</v>
       </c>
       <c r="C114" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D114" t="n">
         <v>34</v>
       </c>
       <c r="E114" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F114" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G114" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I114" t="n">
         <v>51</v>
@@ -4189,15 +4201,15 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C115" t="n">
         <v>49</v>
@@ -4206,16 +4218,16 @@
         <v>39</v>
       </c>
       <c r="E115" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F115" t="n">
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
         <v>55</v>
@@ -4224,36 +4236,36 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B116" t="n">
         <v>52</v>
       </c>
       <c r="C116" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D116" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E116" t="n">
         <v>64</v>
       </c>
       <c r="F116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G116" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H116" t="n">
         <v>7</v>
       </c>
       <c r="I116" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -4263,198 +4275,198 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B117" t="n">
+        <v>62</v>
+      </c>
+      <c r="C117" t="n">
         <v>60</v>
-      </c>
-      <c r="C117" t="n">
-        <v>59</v>
       </c>
       <c r="D117" t="n">
         <v>51</v>
       </c>
       <c r="E117" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F117" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G117" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I117" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J117" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B118" t="n">
         <v>63</v>
       </c>
       <c r="C118" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D118" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E118" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F118" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G118" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H118" t="n">
         <v>6</v>
       </c>
       <c r="I118" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C119" t="n">
         <v>78</v>
       </c>
       <c r="D119" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E119" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F119" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G119" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H119" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I119" t="n">
         <v>75</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B120" t="n">
         <v>100</v>
       </c>
       <c r="C120" t="n">
+        <v>73</v>
+      </c>
+      <c r="D120" t="n">
+        <v>92</v>
+      </c>
+      <c r="E120" t="n">
+        <v>97</v>
+      </c>
+      <c r="F120" t="n">
+        <v>31</v>
+      </c>
+      <c r="G120" t="n">
+        <v>84</v>
+      </c>
+      <c r="H120" t="n">
+        <v>9</v>
+      </c>
+      <c r="I120" t="n">
         <v>74</v>
-      </c>
-      <c r="D120" t="n">
-        <v>89</v>
-      </c>
-      <c r="E120" t="n">
-        <v>95</v>
-      </c>
-      <c r="F120" t="n">
-        <v>30</v>
-      </c>
-      <c r="G120" t="n">
-        <v>81</v>
-      </c>
-      <c r="H120" t="n">
-        <v>10</v>
-      </c>
-      <c r="I120" t="n">
-        <v>75</v>
       </c>
       <c r="J120" t="n">
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C121" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D121" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E121" t="n">
         <v>72</v>
       </c>
       <c r="F121" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G121" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I121" t="n">
         <v>75</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C122" t="n">
         <v>61</v>
       </c>
       <c r="D122" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E122" t="n">
         <v>100</v>
       </c>
       <c r="F122" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G122" t="n">
         <v>100</v>
@@ -4463,21 +4475,21 @@
         <v>8</v>
       </c>
       <c r="I122" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C123" t="n">
         <v>70</v>
@@ -4486,59 +4498,94 @@
         <v>68</v>
       </c>
       <c r="E123" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G123" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H123" t="n">
         <v>8</v>
       </c>
       <c r="I123" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C124" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D124" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E124" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F124" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G124" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H124" t="n">
         <v>9</v>
       </c>
       <c r="I124" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B125" t="n">
+        <v>61</v>
+      </c>
+      <c r="C125" t="n">
+        <v>76</v>
+      </c>
+      <c r="D125" t="n">
+        <v>71</v>
+      </c>
+      <c r="E125" t="n">
+        <v>70</v>
+      </c>
+      <c r="F125" t="n">
+        <v>20</v>
+      </c>
+      <c r="G125" t="n">
+        <v>57</v>
+      </c>
+      <c r="H125" t="n">
+        <v>11</v>
+      </c>
+      <c r="I125" t="n">
+        <v>72</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/plejd_vs_electrician_trends.xlsx
+++ b/data/plejd_vs_electrician_trends.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,72 +417,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Sweden_Plejd</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Sweden_elektriker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Norway_Plejd</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Norway_elektriker</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Finland_Plejd</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Finland_sähköasentaja</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Netherlands_Plejd</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Netherlands_elektricien</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Germany_Plejd</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Germany_Elektriker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>42</v>
@@ -509,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -521,11 +509,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>42</v>
@@ -534,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -552,7 +540,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B4" t="n">
@@ -565,13 +553,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -579,30 +567,30 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -610,11 +598,11 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B6" t="n">
@@ -627,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -645,7 +633,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B7" t="n">
@@ -658,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -676,7 +664,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B8" t="n">
@@ -695,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -703,30 +691,30 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -734,30 +722,30 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
+        <v>41</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>72</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>40</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>71</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>39</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -765,30 +753,30 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -796,30 +784,30 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -827,18 +815,18 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B13" t="n">
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -850,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -858,30 +846,30 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -893,7 +881,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B15" t="n">
@@ -906,13 +894,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -920,15 +908,15 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
         <v>40</v>
@@ -937,13 +925,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -951,30 +939,30 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>54</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>34</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>55</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>32</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -982,11 +970,11 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B18" t="n">
@@ -999,13 +987,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1013,15 +1001,15 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>38</v>
@@ -1030,13 +1018,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1044,11 +1032,11 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B20" t="n">
@@ -1061,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1075,30 +1063,30 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B21" t="n">
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1106,11 +1094,11 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B22" t="n">
@@ -1123,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1137,30 +1125,30 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B23" t="n">
         <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1168,15 +1156,15 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
         <v>46</v>
@@ -1185,13 +1173,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1199,30 +1187,30 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1230,30 +1218,30 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B26" t="n">
         <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1261,15 +1249,15 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
         <v>41</v>
@@ -1292,11 +1280,11 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B28" t="n">
@@ -1309,13 +1297,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1323,30 +1311,30 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1354,11 +1342,11 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B30" t="n">
@@ -1371,13 +1359,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1385,18 +1373,18 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1408,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1420,26 +1408,26 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B32" t="n">
         <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1447,15 +1435,15 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="n">
         <v>43</v>
@@ -1464,13 +1452,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1478,18 +1466,18 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
       </c>
       <c r="C34" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1501,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1513,11 +1501,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C35" t="n">
         <v>48</v>
@@ -1526,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1540,15 +1528,15 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" t="n">
         <v>47</v>
@@ -1563,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1571,30 +1559,30 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B37" t="n">
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1602,11 +1590,11 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B38" t="n">
@@ -1619,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1633,11 +1621,11 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B39" t="n">
@@ -1656,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1664,15 +1652,15 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
         <v>40</v>
@@ -1681,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1695,11 +1683,11 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B41" t="n">
@@ -1712,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1726,11 +1714,11 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B42" t="n">
@@ -1743,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1757,21 +1745,21 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="n">
         <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>62</v>
@@ -1788,11 +1776,11 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B44" t="n">
@@ -1805,13 +1793,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1819,30 +1807,30 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B45" t="n">
         <v>17</v>
       </c>
       <c r="C45" t="n">
+        <v>46</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>73</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
         <v>45</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>74</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>43</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1850,11 +1838,11 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B46" t="n">
@@ -1864,7 +1852,7 @@
         <v>47</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>75</v>
@@ -1873,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1881,18 +1869,18 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B47" t="n">
         <v>26</v>
       </c>
       <c r="C47" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1904,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1912,11 +1900,11 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B48" t="n">
@@ -1929,13 +1917,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1943,15 +1931,15 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" t="n">
         <v>42</v>
@@ -1960,13 +1948,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1974,15 +1962,15 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" t="n">
         <v>49</v>
@@ -1991,13 +1979,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2005,30 +1993,30 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B51" t="n">
         <v>24</v>
       </c>
       <c r="C51" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2036,11 +2024,11 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B52" t="n">
@@ -2050,16 +2038,16 @@
         <v>38</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2067,30 +2055,30 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -2098,11 +2086,11 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B54" t="n">
@@ -2112,16 +2100,16 @@
         <v>42</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -2129,30 +2117,30 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B55" t="n">
         <v>17</v>
       </c>
       <c r="C55" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2160,11 +2148,11 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B56" t="n">
@@ -2183,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -2195,7 +2183,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B57" t="n">
@@ -2205,7 +2193,7 @@
         <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
         <v>78</v>
@@ -2214,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -2222,24 +2210,24 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B58" t="n">
         <v>31</v>
       </c>
       <c r="C58" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -2253,30 +2241,30 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B59" t="n">
         <v>39</v>
       </c>
       <c r="C59" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D59" t="n">
         <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -2284,21 +2272,21 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B60" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C60" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
         <v>81</v>
@@ -2307,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2315,30 +2303,30 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B61" t="n">
         <v>40</v>
       </c>
       <c r="C61" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
         <v>65</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2346,11 +2334,11 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B62" t="n">
@@ -2363,33 +2351,33 @@
         <v>5</v>
       </c>
       <c r="E62" t="n">
+        <v>76</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>58</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>73</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>78</v>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>57</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>71</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>74</v>
-      </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C63" t="n">
         <v>51</v>
@@ -2398,36 +2386,36 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B64" t="n">
         <v>32</v>
       </c>
       <c r="C64" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D64" t="n">
         <v>5</v>
@@ -2436,68 +2424,68 @@
         <v>66</v>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D65" t="n">
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B66" t="n">
         <v>27</v>
       </c>
       <c r="C66" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
         <v>4</v>
@@ -2509,36 +2497,36 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B67" t="n">
         <v>26</v>
       </c>
       <c r="C67" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D67" t="n">
         <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2550,27 +2538,27 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C68" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
         <v>63</v>
@@ -2579,23 +2567,23 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B69" t="n">
@@ -2608,33 +2596,33 @@
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C70" t="n">
         <v>58</v>
@@ -2643,10 +2631,10 @@
         <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G70" t="n">
         <v>62</v>
@@ -2655,17 +2643,17 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B71" t="n">
@@ -2675,16 +2663,16 @@
         <v>56</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2696,11 +2684,11 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B72" t="n">
@@ -2713,71 +2701,71 @@
         <v>10</v>
       </c>
       <c r="E72" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C73" t="n">
         <v>47</v>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E73" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B74" t="n">
         <v>52</v>
       </c>
       <c r="C74" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D74" t="n">
         <v>13</v>
@@ -2786,30 +2774,30 @@
         <v>92</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C75" t="n">
         <v>51</v>
@@ -2824,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -2840,7 +2828,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B76" t="n">
@@ -2853,77 +2841,77 @@
         <v>11</v>
       </c>
       <c r="E76" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F76" t="n">
         <v>7</v>
       </c>
       <c r="G76" t="n">
+        <v>73</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
         <v>71</v>
       </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>69</v>
-      </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C77" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E77" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B78" t="n">
         <v>25</v>
       </c>
       <c r="C78" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E78" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F78" t="n">
         <v>4</v>
@@ -2935,56 +2923,56 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C79" t="n">
         <v>46</v>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B80" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C80" t="n">
         <v>47</v>
@@ -2996,7 +2984,7 @@
         <v>61</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
         <v>46</v>
@@ -3011,50 +2999,50 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C81" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D81" t="n">
         <v>15</v>
       </c>
       <c r="E81" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G81" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C82" t="n">
         <v>58</v>
@@ -3066,30 +3054,30 @@
         <v>90</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G82" t="n">
         <v>74</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C83" t="n">
         <v>61</v>
@@ -3101,208 +3089,208 @@
         <v>90</v>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G83" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B84" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C84" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E84" t="n">
         <v>86</v>
       </c>
       <c r="F84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G84" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C85" t="n">
         <v>55</v>
       </c>
       <c r="D85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G85" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C86" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D86" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E86" t="n">
+        <v>85</v>
+      </c>
+      <c r="F86" t="n">
+        <v>11</v>
+      </c>
+      <c r="G86" t="n">
+        <v>66</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>83</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>86</v>
       </c>
-      <c r="F86" t="n">
-        <v>8</v>
-      </c>
-      <c r="G86" t="n">
-        <v>64</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>81</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>89</v>
-      </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C87" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D87" t="n">
         <v>18</v>
       </c>
       <c r="E87" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G87" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C88" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D88" t="n">
         <v>18</v>
       </c>
       <c r="E88" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G88" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B89" t="n">
         <v>28</v>
       </c>
       <c r="C89" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D89" t="n">
         <v>14</v>
@@ -3311,16 +3299,16 @@
         <v>63</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G89" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3330,11 +3318,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C90" t="n">
         <v>54</v>
@@ -3346,65 +3334,65 @@
         <v>74</v>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I90" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B91" t="n">
         <v>23</v>
       </c>
       <c r="C91" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D91" t="n">
         <v>17</v>
       </c>
       <c r="E91" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C92" t="n">
         <v>45</v>
@@ -3416,26 +3404,26 @@
         <v>63</v>
       </c>
       <c r="F92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B93" t="n">
@@ -3445,39 +3433,39 @@
         <v>52</v>
       </c>
       <c r="D93" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E93" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C94" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D94" t="n">
         <v>25</v>
@@ -3486,61 +3474,61 @@
         <v>86</v>
       </c>
       <c r="F94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G94" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C95" t="n">
         <v>58</v>
       </c>
       <c r="D95" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E95" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F95" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G95" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B96" t="n">
@@ -3553,16 +3541,16 @@
         <v>40</v>
       </c>
       <c r="E96" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G96" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
         <v>63</v>
@@ -3571,151 +3559,151 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C97" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D97" t="n">
         <v>30</v>
       </c>
       <c r="E97" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G97" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C98" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D98" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E98" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H98" t="n">
         <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D99" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E99" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F99" t="n">
         <v>13</v>
       </c>
       <c r="G99" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B100" t="n">
         <v>35</v>
       </c>
       <c r="C100" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D100" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E100" t="n">
         <v>66</v>
       </c>
       <c r="F100" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G100" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B101" t="n">
@@ -3728,39 +3716,39 @@
         <v>24</v>
       </c>
       <c r="E101" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F101" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G101" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
       </c>
       <c r="I101" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C102" t="n">
         <v>47</v>
       </c>
       <c r="D102" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E102" t="n">
         <v>63</v>
@@ -3772,7 +3760,7 @@
         <v>56</v>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I102" t="n">
         <v>51</v>
@@ -3781,106 +3769,106 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C103" t="n">
         <v>45</v>
       </c>
       <c r="D103" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E103" t="n">
         <v>66</v>
       </c>
       <c r="F103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
         <v>44</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I103" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C104" t="n">
         <v>42</v>
       </c>
       <c r="D104" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E104" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G104" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I104" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B105" t="n">
         <v>43</v>
       </c>
       <c r="C105" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D105" t="n">
         <v>32</v>
       </c>
       <c r="E105" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F105" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G105" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -3890,67 +3878,67 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B106" t="n">
         <v>52</v>
       </c>
       <c r="C106" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D106" t="n">
         <v>42</v>
       </c>
       <c r="E106" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G106" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H106" t="n">
         <v>4</v>
       </c>
       <c r="I106" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C107" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D107" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E107" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F107" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G107" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I107" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -3960,7 +3948,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B108" t="n">
@@ -3976,65 +3964,65 @@
         <v>89</v>
       </c>
       <c r="F108" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G108" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
+        <v>68</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B109" t="n">
+        <v>70</v>
+      </c>
+      <c r="C109" t="n">
+        <v>46</v>
+      </c>
+      <c r="D109" t="n">
+        <v>62</v>
+      </c>
+      <c r="E109" t="n">
         <v>67</v>
       </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B109" t="n">
-        <v>69</v>
-      </c>
-      <c r="C109" t="n">
-        <v>45</v>
-      </c>
-      <c r="D109" t="n">
-        <v>63</v>
-      </c>
-      <c r="E109" t="n">
-        <v>66</v>
-      </c>
       <c r="F109" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G109" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H109" t="n">
         <v>5</v>
       </c>
       <c r="I109" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C110" t="n">
         <v>59</v>
@@ -4043,141 +4031,141 @@
         <v>56</v>
       </c>
       <c r="E110" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F110" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G110" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H110" t="n">
         <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C111" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D111" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E111" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F111" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G111" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H111" t="n">
         <v>5</v>
       </c>
       <c r="I111" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C112" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D112" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E112" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G112" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I112" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C113" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D113" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E113" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F113" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G113" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H113" t="n">
         <v>4</v>
       </c>
       <c r="I113" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C114" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D114" t="n">
         <v>34</v>
@@ -4186,30 +4174,30 @@
         <v>71</v>
       </c>
       <c r="F114" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G114" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H114" t="n">
         <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C115" t="n">
         <v>49</v>
@@ -4218,134 +4206,134 @@
         <v>39</v>
       </c>
       <c r="E115" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F115" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G115" t="n">
+        <v>54</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>57</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B116" t="n">
         <v>53</v>
-      </c>
-      <c r="H115" t="n">
-        <v>3</v>
-      </c>
-      <c r="I115" t="n">
-        <v>55</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>45869</v>
-      </c>
-      <c r="B116" t="n">
-        <v>52</v>
       </c>
       <c r="C116" t="n">
         <v>47</v>
       </c>
       <c r="D116" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E116" t="n">
         <v>64</v>
       </c>
       <c r="F116" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G116" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H116" t="n">
         <v>7</v>
       </c>
       <c r="I116" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C117" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D117" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E117" t="n">
         <v>87</v>
       </c>
       <c r="F117" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G117" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H117" t="n">
         <v>5</v>
       </c>
       <c r="I117" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J117" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C118" t="n">
         <v>71</v>
       </c>
       <c r="D118" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E118" t="n">
         <v>93</v>
       </c>
       <c r="F118" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G118" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I118" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B119" t="n">
@@ -4355,22 +4343,22 @@
         <v>78</v>
       </c>
       <c r="D119" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E119" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F119" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G119" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H119" t="n">
         <v>7</v>
       </c>
       <c r="I119" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -4380,17 +4368,17 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B120" t="n">
         <v>100</v>
       </c>
       <c r="C120" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D120" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E120" t="n">
         <v>97</v>
@@ -4399,23 +4387,23 @@
         <v>31</v>
       </c>
       <c r="G120" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H120" t="n">
         <v>9</v>
       </c>
       <c r="I120" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J120" t="n">
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B121" t="n">
@@ -4425,67 +4413,67 @@
         <v>64</v>
       </c>
       <c r="D121" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E121" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F121" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G121" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
       </c>
       <c r="I121" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B122" t="n">
         <v>70</v>
       </c>
       <c r="C122" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D122" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E122" t="n">
         <v>100</v>
       </c>
       <c r="F122" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G122" t="n">
         <v>100</v>
       </c>
       <c r="H122" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I122" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B123" t="n">
@@ -4495,16 +4483,16 @@
         <v>70</v>
       </c>
       <c r="D123" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E123" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F123" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G123" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H123" t="n">
         <v>8</v>
@@ -4513,33 +4501,33 @@
         <v>79</v>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B124" t="n">
         <v>54</v>
       </c>
       <c r="C124" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D124" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E124" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F124" t="n">
         <v>17</v>
       </c>
       <c r="G124" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H124" t="n">
         <v>9</v>
@@ -4551,42 +4539,77 @@
         <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B125" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C125" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D125" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E125" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F125" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G125" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="H125" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I125" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>100</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" t="n">
+        <v>48</v>
+      </c>
+      <c r="C126" t="n">
+        <v>58</v>
+      </c>
+      <c r="D126" t="n">
+        <v>51</v>
+      </c>
+      <c r="E126" t="n">
+        <v>75</v>
+      </c>
+      <c r="F126" t="n">
+        <v>12</v>
+      </c>
+      <c r="G126" t="n">
+        <v>69</v>
+      </c>
+      <c r="H126" t="n">
+        <v>7</v>
+      </c>
+      <c r="I126" t="n">
+        <v>69</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/plejd_vs_electrician_trends.xlsx
+++ b/data/plejd_vs_electrician_trends.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,72 +429,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Sweden_Plejd</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Sweden_elektriker</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Norway_Plejd</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Norway_elektriker</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Finland_Plejd</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Finland_sähköasentaja</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Netherlands_Plejd</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Netherlands_elektricien</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Germany_Plejd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Germany_Elektriker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>42</v>
@@ -491,13 +503,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -505,30 +517,30 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -536,11 +548,11 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B4" t="n">
@@ -553,13 +565,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -567,11 +579,11 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B5" t="n">
@@ -584,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -598,24 +610,24 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -629,11 +641,11 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B7" t="n">
@@ -646,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -660,11 +672,11 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B8" t="n">
@@ -677,13 +689,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -691,15 +703,15 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>39</v>
@@ -708,13 +720,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -722,11 +734,11 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B10" t="n">
@@ -739,13 +751,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -753,11 +765,11 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B11" t="n">
@@ -770,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -784,24 +796,24 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -815,30 +827,30 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B13" t="n">
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -846,11 +858,11 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B14" t="n">
@@ -863,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -877,11 +889,11 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B15" t="n">
@@ -894,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -908,27 +920,27 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>42</v>
@@ -939,30 +951,30 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -970,11 +982,11 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B18" t="n">
@@ -987,13 +999,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1001,11 +1013,11 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B19" t="n">
@@ -1018,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1032,11 +1044,11 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B20" t="n">
@@ -1049,13 +1061,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1063,11 +1075,11 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B21" t="n">
@@ -1080,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1094,11 +1106,11 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B22" t="n">
@@ -1111,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1125,11 +1137,11 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B23" t="n">
@@ -1142,13 +1154,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1156,30 +1168,30 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B24" t="n">
         <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1187,30 +1199,30 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B25" t="n">
         <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1218,30 +1230,30 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B26" t="n">
         <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1249,30 +1261,30 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1280,11 +1292,11 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B28" t="n">
@@ -1297,13 +1309,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1311,30 +1323,30 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1342,30 +1354,30 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B30" t="n">
         <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1373,24 +1385,24 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B31" t="n">
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1404,11 +1416,11 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B32" t="n">
@@ -1421,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1435,30 +1447,30 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
       </c>
       <c r="C33" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1466,30 +1478,30 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
       </c>
       <c r="C34" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1497,15 +1509,15 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C35" t="n">
         <v>48</v>
@@ -1514,13 +1526,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1528,30 +1540,30 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1559,11 +1571,11 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B37" t="n">
@@ -1576,13 +1588,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1590,11 +1602,11 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B38" t="n">
@@ -1607,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1621,11 +1633,11 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B39" t="n">
@@ -1638,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1652,15 +1664,15 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" t="n">
         <v>40</v>
@@ -1669,13 +1681,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1683,11 +1695,11 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B41" t="n">
@@ -1700,13 +1712,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1714,11 +1726,11 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B42" t="n">
@@ -1731,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1745,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B43" t="n">
@@ -1759,16 +1771,16 @@
         <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1776,11 +1788,11 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B44" t="n">
@@ -1793,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1807,24 +1819,24 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B45" t="n">
         <v>17</v>
       </c>
       <c r="C45" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1838,30 +1850,30 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C46" t="n">
         <v>47</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1869,30 +1881,30 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B47" t="n">
         <v>26</v>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1900,11 +1912,11 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B48" t="n">
@@ -1917,13 +1929,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1931,11 +1943,11 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B49" t="n">
@@ -1948,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1962,15 +1974,15 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C50" t="n">
         <v>49</v>
@@ -1979,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F50" t="n">
         <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1993,27 +2005,27 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B51" t="n">
         <v>24</v>
       </c>
       <c r="C51" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>56</v>
@@ -2024,11 +2036,11 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B52" t="n">
@@ -2038,16 +2050,16 @@
         <v>38</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2055,24 +2067,24 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B53" t="n">
         <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2086,11 +2098,11 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B54" t="n">
@@ -2100,10 +2112,10 @@
         <v>42</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2117,30 +2129,30 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>44012</v>
+      </c>
+      <c r="B55" t="n">
+        <v>18</v>
+      </c>
+      <c r="C55" t="n">
+        <v>47</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
         <v>62</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>44012</v>
-      </c>
-      <c r="B55" t="n">
-        <v>17</v>
-      </c>
-      <c r="C55" t="n">
-        <v>48</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>66</v>
-      </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2148,30 +2160,30 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B56" t="n">
         <v>22</v>
       </c>
       <c r="C56" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -2179,11 +2191,11 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B57" t="n">
@@ -2193,10 +2205,10 @@
         <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2210,30 +2222,30 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B58" t="n">
         <v>31</v>
       </c>
       <c r="C58" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2241,11 +2253,11 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B59" t="n">
@@ -2258,13 +2270,13 @@
         <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -2272,11 +2284,11 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B60" t="n">
@@ -2286,16 +2298,16 @@
         <v>55</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2303,30 +2315,30 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B61" t="n">
         <v>40</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D61" t="n">
+        <v>5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>60</v>
+      </c>
+      <c r="F61" t="n">
         <v>6</v>
       </c>
-      <c r="E61" t="n">
-        <v>65</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2334,94 +2346,94 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B62" t="n">
         <v>35</v>
       </c>
       <c r="C62" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D62" t="n">
         <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C63" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D63" t="n">
         <v>7</v>
       </c>
       <c r="E63" t="n">
+        <v>71</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>62</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>55</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>76</v>
       </c>
-      <c r="F63" t="n">
-        <v>8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>64</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>56</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>79</v>
-      </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B64" t="n">
         <v>32</v>
       </c>
       <c r="C64" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
@@ -2439,11 +2451,11 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B65" t="n">
@@ -2456,29 +2468,29 @@
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B66" t="n">
@@ -2488,36 +2500,36 @@
         <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C67" t="n">
         <v>48</v>
@@ -2526,29 +2538,29 @@
         <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B68" t="n">
@@ -2558,45 +2570,45 @@
         <v>43</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B69" t="n">
         <v>30</v>
       </c>
       <c r="C69" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2608,21 +2620,21 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C70" t="n">
         <v>58</v>
@@ -2631,10 +2643,10 @@
         <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G70" t="n">
         <v>62</v>
@@ -2643,17 +2655,17 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B71" t="n">
@@ -2666,13 +2678,13 @@
         <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2684,116 +2696,116 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B72" t="n">
         <v>51</v>
       </c>
       <c r="C72" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D72" t="n">
         <v>10</v>
       </c>
       <c r="E72" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G72" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C73" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="n">
+        <v>60</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>58</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>71</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B74" t="n">
+        <v>51</v>
+      </c>
+      <c r="C74" t="n">
+        <v>54</v>
+      </c>
+      <c r="D74" t="n">
         <v>11</v>
       </c>
-      <c r="E73" t="n">
-        <v>65</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>57</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>73</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
+      <c r="E74" t="n">
+        <v>87</v>
+      </c>
+      <c r="F74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" t="n">
         <v>68</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>44592</v>
-      </c>
-      <c r="B74" t="n">
-        <v>52</v>
-      </c>
-      <c r="C74" t="n">
-        <v>55</v>
-      </c>
-      <c r="D74" t="n">
-        <v>13</v>
-      </c>
-      <c r="E74" t="n">
-        <v>92</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>67</v>
-      </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B75" t="n">
@@ -2803,32 +2815,32 @@
         <v>51</v>
       </c>
       <c r="D75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B76" t="n">
@@ -2838,13 +2850,13 @@
         <v>52</v>
       </c>
       <c r="D76" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G76" t="n">
         <v>73</v>
@@ -2853,36 +2865,36 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C77" t="n">
         <v>49</v>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E77" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F77" t="n">
         <v>4</v>
       </c>
       <c r="G77" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2894,11 +2906,11 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B78" t="n">
@@ -2911,7 +2923,7 @@
         <v>9</v>
       </c>
       <c r="E78" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F78" t="n">
         <v>4</v>
@@ -2923,17 +2935,17 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B79" t="n">
@@ -2943,32 +2955,32 @@
         <v>46</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B80" t="n">
@@ -2978,13 +2990,13 @@
         <v>47</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E80" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>46</v>
@@ -2993,36 +3005,36 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B81" t="n">
         <v>39</v>
       </c>
       <c r="C81" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E81" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3034,46 +3046,46 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B82" t="n">
         <v>43</v>
       </c>
       <c r="C82" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D82" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B83" t="n">
@@ -3083,32 +3095,32 @@
         <v>61</v>
       </c>
       <c r="D83" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E83" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F83" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B84" t="n">
@@ -3118,45 +3130,45 @@
         <v>58</v>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E84" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F84" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G84" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B85" t="n">
         <v>49</v>
       </c>
       <c r="C85" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D85" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E85" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F85" t="n">
         <v>11</v>
@@ -3168,122 +3180,122 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C86" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D86" t="n">
         <v>17</v>
       </c>
       <c r="E86" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G86" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C87" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D87" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F87" t="n">
         <v>12</v>
       </c>
       <c r="G87" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C88" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D88" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E88" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G88" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H88" t="n">
         <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B89" t="n">
@@ -3296,29 +3308,29 @@
         <v>14</v>
       </c>
       <c r="E89" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B90" t="n">
@@ -3328,32 +3340,32 @@
         <v>54</v>
       </c>
       <c r="D90" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F90" t="n">
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B91" t="n">
@@ -3363,13 +3375,13 @@
         <v>52</v>
       </c>
       <c r="D91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
         <v>56</v>
@@ -3384,11 +3396,11 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B92" t="n">
@@ -3398,67 +3410,67 @@
         <v>45</v>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E92" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G92" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H92" t="n">
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C93" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D93" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E93" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F93" t="n">
         <v>10</v>
       </c>
       <c r="G93" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B94" t="n">
@@ -3468,10 +3480,10 @@
         <v>55</v>
       </c>
       <c r="D94" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E94" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F94" t="n">
         <v>13</v>
@@ -3483,30 +3495,30 @@
         <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C95" t="n">
         <v>58</v>
       </c>
       <c r="D95" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E95" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F95" t="n">
         <v>14</v>
@@ -3518,17 +3530,17 @@
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B96" t="n">
@@ -3538,45 +3550,45 @@
         <v>60</v>
       </c>
       <c r="D96" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E96" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F96" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G96" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H96" t="n">
         <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B97" t="n">
         <v>51</v>
       </c>
       <c r="C97" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D97" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E97" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F97" t="n">
         <v>10</v>
@@ -3588,52 +3600,52 @@
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98" t="n">
         <v>56</v>
       </c>
       <c r="D98" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E98" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G98" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B99" t="n">
@@ -3643,45 +3655,45 @@
         <v>51</v>
       </c>
       <c r="D99" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E99" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F99" t="n">
         <v>13</v>
       </c>
       <c r="G99" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B100" t="n">
         <v>35</v>
       </c>
       <c r="C100" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D100" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E100" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F100" t="n">
         <v>12</v>
@@ -3693,52 +3705,52 @@
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B101" t="n">
         <v>36</v>
       </c>
       <c r="C101" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D101" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E101" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F101" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G101" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
       </c>
       <c r="I101" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B102" t="n">
@@ -3748,16 +3760,16 @@
         <v>47</v>
       </c>
       <c r="D102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E102" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
@@ -3769,24 +3781,24 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B103" t="n">
         <v>29</v>
       </c>
       <c r="C103" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D103" t="n">
         <v>26</v>
       </c>
       <c r="E103" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F103" t="n">
         <v>10</v>
@@ -3798,17 +3810,17 @@
         <v>3</v>
       </c>
       <c r="I103" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B104" t="n">
@@ -3818,32 +3830,32 @@
         <v>42</v>
       </c>
       <c r="D104" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E104" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G104" t="n">
         <v>47</v>
       </c>
       <c r="H104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I104" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B105" t="n">
@@ -3853,19 +3865,19 @@
         <v>52</v>
       </c>
       <c r="D105" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E105" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F105" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G105" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
         <v>53</v>
@@ -3874,11 +3886,11 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B106" t="n">
@@ -3888,16 +3900,16 @@
         <v>54</v>
       </c>
       <c r="D106" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E106" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F106" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G106" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H106" t="n">
         <v>4</v>
@@ -3909,46 +3921,46 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B107" t="n">
+        <v>65</v>
+      </c>
+      <c r="C107" t="n">
+        <v>59</v>
+      </c>
+      <c r="D107" t="n">
+        <v>43</v>
+      </c>
+      <c r="E107" t="n">
+        <v>86</v>
+      </c>
+      <c r="F107" t="n">
+        <v>16</v>
+      </c>
+      <c r="G107" t="n">
         <v>64</v>
       </c>
-      <c r="C107" t="n">
-        <v>58</v>
-      </c>
-      <c r="D107" t="n">
-        <v>46</v>
-      </c>
-      <c r="E107" t="n">
-        <v>90</v>
-      </c>
-      <c r="F107" t="n">
-        <v>21</v>
-      </c>
-      <c r="G107" t="n">
-        <v>63</v>
-      </c>
       <c r="H107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I107" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B108" t="n">
@@ -3958,19 +3970,19 @@
         <v>55</v>
       </c>
       <c r="D108" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E108" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F108" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G108" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I108" t="n">
         <v>68</v>
@@ -3979,11 +3991,11 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B109" t="n">
@@ -3993,16 +4005,16 @@
         <v>46</v>
       </c>
       <c r="D109" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E109" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F109" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G109" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H109" t="n">
         <v>5</v>
@@ -4014,81 +4026,81 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C110" t="n">
         <v>59</v>
       </c>
       <c r="D110" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E110" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F110" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G110" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H110" t="n">
         <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B111" t="n">
         <v>52</v>
       </c>
       <c r="C111" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D111" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E111" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F111" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G111" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H111" t="n">
         <v>5</v>
       </c>
       <c r="I111" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B112" t="n">
@@ -4098,32 +4110,32 @@
         <v>54</v>
       </c>
       <c r="D112" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E112" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F112" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G112" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H112" t="n">
         <v>4</v>
       </c>
       <c r="I112" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B113" t="n">
@@ -4133,242 +4145,242 @@
         <v>49</v>
       </c>
       <c r="D113" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E113" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F113" t="n">
         <v>18</v>
       </c>
       <c r="G113" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H113" t="n">
         <v>4</v>
       </c>
       <c r="I113" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B114" t="n">
         <v>43</v>
       </c>
       <c r="C114" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D114" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E114" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F114" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G114" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H114" t="n">
         <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C115" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D115" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E115" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H115" t="n">
         <v>4</v>
       </c>
       <c r="I115" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C116" t="n">
         <v>47</v>
       </c>
       <c r="D116" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E116" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F116" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H116" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I116" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C117" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D117" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E117" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G117" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H117" t="n">
         <v>5</v>
       </c>
       <c r="I117" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J117" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C118" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D118" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E118" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F118" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G118" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I118" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C119" t="n">
         <v>78</v>
       </c>
       <c r="D119" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E119" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F119" t="n">
         <v>32</v>
       </c>
       <c r="G119" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I119" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B120" t="n">
@@ -4378,48 +4390,48 @@
         <v>74</v>
       </c>
       <c r="D120" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E120" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F120" t="n">
         <v>31</v>
       </c>
       <c r="G120" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H120" t="n">
         <v>9</v>
       </c>
       <c r="I120" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J120" t="n">
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C121" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D121" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E121" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F121" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G121" t="n">
         <v>62</v>
@@ -4428,30 +4440,30 @@
         <v>9</v>
       </c>
       <c r="I121" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C122" t="n">
         <v>62</v>
       </c>
       <c r="D122" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E122" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F122" t="n">
         <v>28</v>
@@ -4463,17 +4475,17 @@
         <v>7</v>
       </c>
       <c r="I122" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B123" t="n">
@@ -4483,13 +4495,13 @@
         <v>70</v>
       </c>
       <c r="D123" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E123" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F123" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G123" t="n">
         <v>88</v>
@@ -4498,17 +4510,17 @@
         <v>8</v>
       </c>
       <c r="I123" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B124" t="n">
@@ -4518,48 +4530,48 @@
         <v>62</v>
       </c>
       <c r="D124" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E124" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F124" t="n">
         <v>17</v>
       </c>
       <c r="G124" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H124" t="n">
         <v>9</v>
       </c>
       <c r="I124" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J124" t="n">
         <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B125" t="n">
         <v>57</v>
       </c>
       <c r="C125" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D125" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E125" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F125" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G125" t="n">
         <v>69</v>
@@ -4568,48 +4580,188 @@
         <v>9</v>
       </c>
       <c r="I125" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J125" t="n">
         <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B126" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C126" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D126" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E126" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F126" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G126" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H126" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I126" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J126" t="n">
         <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>89</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B127" t="n">
+        <v>41</v>
+      </c>
+      <c r="C127" t="n">
+        <v>60</v>
+      </c>
+      <c r="D127" t="n">
+        <v>44</v>
+      </c>
+      <c r="E127" t="n">
+        <v>75</v>
+      </c>
+      <c r="F127" t="n">
+        <v>14</v>
+      </c>
+      <c r="G127" t="n">
+        <v>61</v>
+      </c>
+      <c r="H127" t="n">
+        <v>9</v>
+      </c>
+      <c r="I127" t="n">
+        <v>64</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B128" t="n">
+        <v>45</v>
+      </c>
+      <c r="C128" t="n">
+        <v>48</v>
+      </c>
+      <c r="D128" t="n">
+        <v>44</v>
+      </c>
+      <c r="E128" t="n">
+        <v>62</v>
+      </c>
+      <c r="F128" t="n">
+        <v>15</v>
+      </c>
+      <c r="G128" t="n">
+        <v>50</v>
+      </c>
+      <c r="H128" t="n">
+        <v>10</v>
+      </c>
+      <c r="I128" t="n">
+        <v>64</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B129" t="n">
+        <v>60</v>
+      </c>
+      <c r="C129" t="n">
+        <v>63</v>
+      </c>
+      <c r="D129" t="n">
+        <v>61</v>
+      </c>
+      <c r="E129" t="n">
+        <v>84</v>
+      </c>
+      <c r="F129" t="n">
+        <v>19</v>
+      </c>
+      <c r="G129" t="n">
+        <v>63</v>
+      </c>
+      <c r="H129" t="n">
+        <v>7</v>
+      </c>
+      <c r="I129" t="n">
+        <v>53</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B130" t="n">
+        <v>67</v>
+      </c>
+      <c r="C130" t="n">
+        <v>76</v>
+      </c>
+      <c r="D130" t="n">
+        <v>70</v>
+      </c>
+      <c r="E130" t="n">
+        <v>100</v>
+      </c>
+      <c r="F130" t="n">
+        <v>26</v>
+      </c>
+      <c r="G130" t="n">
+        <v>97</v>
+      </c>
+      <c r="H130" t="n">
+        <v>8</v>
+      </c>
+      <c r="I130" t="n">
+        <v>72</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
